--- a/target/classes/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C599A818-6331-4304-B6D6-511DC2CDDE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3485E5C9-0A6E-4E18-911D-A777C0D56159}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F173C3BF-BF45-4085-9BA4-BD846F4D371B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F173C3BF-BF45-4085-9BA4-BD846F4D371B}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIOS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,12 +23,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>USUARIO</t>
   </si>
@@ -50,18 +45,12 @@
     <t>rstadmin</t>
   </si>
   <si>
-    <t>mluisa</t>
-  </si>
-  <si>
     <t>moonsky</t>
   </si>
   <si>
     <t>avargas</t>
   </si>
   <si>
-    <t>luffyonepiece</t>
-  </si>
-  <si>
     <t>NOMBRE</t>
   </si>
   <si>
@@ -71,9 +60,6 @@
     <t>Desarrollador</t>
   </si>
   <si>
-    <t>Adderly</t>
-  </si>
-  <si>
     <t>Facturista</t>
   </si>
   <si>
@@ -98,12 +84,6 @@
     <t>angel@gmail.com</t>
   </si>
   <si>
-    <t>1234</t>
-  </si>
-  <si>
-    <t>AUXILIAR</t>
-  </si>
-  <si>
     <t>angelLira210</t>
   </si>
   <si>
@@ -114,16 +94,51 @@
   </si>
   <si>
     <t>Luis Angel Lira</t>
+  </si>
+  <si>
+    <t>vargas90</t>
+  </si>
+  <si>
+    <t>Adderly Vargas</t>
+  </si>
+  <si>
+    <t>Ventas</t>
+  </si>
+  <si>
+    <t>avargas@gmail.com</t>
+  </si>
+  <si>
+    <t>lmartinez@gmail.com</t>
+  </si>
+  <si>
+    <t>jflores@gmail.com</t>
+  </si>
+  <si>
+    <t>Programador</t>
+  </si>
+  <si>
+    <t>Director Finanzas</t>
+  </si>
+  <si>
+    <t>lmartinez</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -146,13 +161,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -486,14 +504,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259A3497-F28F-45C5-97D9-93E4AAFCB59D}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="26.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.296875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="27.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,36 +523,36 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -538,64 +560,84 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{5E5034FA-D784-49B2-A6C5-D7012E960578}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{065FB047-14EE-4265-839B-DA3E7AD56F55}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{43CDEE9E-7F8D-4838-9C56-4B293D1F326B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>